--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202608/Category_P&L_20260820.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202608/Category_P&L_20260820.xlsx
@@ -45449,25 +45449,25 @@
         <v>46253</v>
       </c>
       <c r="B1186">
-        <v>94261905.13</v>
+        <v>93321892.78</v>
       </c>
       <c r="C1186">
-        <v>-2917021.68</v>
+        <v>-909659.21</v>
       </c>
       <c r="D1186">
-        <v>-0.030946</v>
+        <v>-0.009650000000000001</v>
       </c>
       <c r="E1186">
-        <v>4577.6</v>
+        <v>9190.299999999999</v>
       </c>
       <c r="F1186">
-        <v>4.9E-05</v>
+        <v>9.7E-05</v>
       </c>
       <c r="G1186">
-        <v>-193</v>
+        <v>39</v>
       </c>
       <c r="H1186">
-        <v>-2E-06</v>
+        <v>0</v>
       </c>
       <c r="I1186">
         <v>0</v>
@@ -45493,7 +45493,7 @@
         <v>-645785.8</v>
       </c>
       <c r="D1187">
-        <v>-0.006851</v>
+        <v>-0.00692</v>
       </c>
       <c r="E1187">
         <v>-13.5</v>
